--- a/src/ComponentService.Web/wwwroot/excel_template/Import_Item_temp.xlsx
+++ b/src/ComponentService.Web/wwwroot/excel_template/Import_Item_temp.xlsx
@@ -1,34 +1,244 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c40552de5c3f05e0/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FF98BE4-C0E1-4041-A1BB-2460554633E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="สินค้า" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>isiri</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{73FB34B0-0A5A-43E1-AB86-36425E5F302B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">สูงสุด 12 ตัวอักษร
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{3DCB45B2-45A8-4C9A-A775-73A2999B3337}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">สูงสุด 100 ตัวอักษร
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{6AE19851-4AFA-47E9-A002-08E1906328FF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>Case
+Film
+Equipment</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{FC07D55A-D75D-4FE6-BCCA-FBF5FAE03341}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>IPHONE
+SAMSUNG
+OPPO
+VIVO
+REALME
+HUAWEI
+RELIFE
+NONE
+* ถ้าไม่มีให้ใส่ NONE อย่าปล่อยว่าง
+** ถ้ามีนอกเหนือจากนี้ต้องดูในระบบยึดตามระบบ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{8C2BE274-17DA-40F4-ABFD-7CE1D99A5FB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>ถ้าไม่มีให้ใส่ 0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{0CB6C79A-B97D-4024-AB19-9E990A2EF8D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>ถ้าไม่มีให้ใส่ 0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{1A2DA5A2-A4A9-45F1-A3DD-BBE2AD278FAE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>ถ้าไม่มีให้ใส่ 0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{49733259-ADE8-4BDA-A047-E3B2CB675FE5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>ถ้าไม่มีให้ใส่ 0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{A6B4BFA4-C1F1-47EF-B378-CAD01594AE62}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>ถ้าไม่มีให้ใส่ 0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{A9F0988C-9B0E-4D10-A212-327B84D0A610}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">สูงสุด 300 ตัวอักษร
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>รหัสสินค้า</t>
   </si>
@@ -57,26 +267,14 @@
     <t>รายละเอียด</t>
   </si>
   <si>
-    <t>HW3I</t>
-  </si>
-  <si>
-    <t>CASE</t>
-  </si>
-  <si>
-    <t>HUAWEI</t>
-  </si>
-  <si>
-    <t>CASE HW NOVA 3i</t>
-  </si>
-  <si>
-    <t>รายละเอียดที่ต้องการ</t>
+    <t>จำนวนสูงสุด</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +282,19 @@
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
     </font>
   </fonts>
   <fills count="3">
@@ -470,30 +681,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.08203125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.58203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="8.25" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.58203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.625" style="4"/>
+    <col min="9" max="9" width="11.33203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="17.08203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.58203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="28.5">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,276 +731,259 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="5">
-        <v>200</v>
-      </c>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F2" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G2" s="6">
-        <v>100</v>
-      </c>
-      <c r="H2" s="5">
-        <v>10</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="6:7">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="6:7">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="6:7">
+    <row r="19" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="6:7">
+    <row r="20" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" spans="6:7">
+    <row r="21" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="6:7">
+    <row r="22" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="6:7">
+    <row r="23" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="6:7">
+    <row r="24" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="6:7">
+    <row r="25" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="6:7">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="6:7">
+    <row r="27" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="6:7">
+    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="6:7">
+    <row r="29" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="6:7">
+    <row r="30" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="6:7">
+    <row r="31" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="6:7">
+    <row r="32" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
     </row>
-    <row r="33" spans="6:7">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
     </row>
-    <row r="34" spans="6:7">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="6:7">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="36" spans="6:7">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
     </row>
-    <row r="37" spans="6:7">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
     </row>
-    <row r="38" spans="6:7">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
     </row>
-    <row r="39" spans="6:7">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="6:7">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
     </row>
-    <row r="41" spans="6:7">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
     </row>
-    <row r="42" spans="6:7">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
     </row>
-    <row r="43" spans="6:7">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="6:7">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="45" spans="6:7">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
     </row>
-    <row r="46" spans="6:7">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
     </row>
-    <row r="47" spans="6:7">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
     </row>
-    <row r="48" spans="6:7">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
     </row>
-    <row r="49" spans="6:7">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="6:7">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
     </row>
-    <row r="51" spans="6:7">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
     </row>
-    <row r="52" spans="6:7">
+    <row r="52" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
     </row>
-    <row r="53" spans="6:7">
+    <row r="53" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
     </row>
-    <row r="54" spans="6:7">
+    <row r="54" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
     </row>
-    <row r="55" spans="6:7">
+    <row r="55" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="6:7">
+    <row r="56" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="6:7">
+    <row r="57" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
     </row>
-    <row r="58" spans="6:7">
+    <row r="58" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
     </row>
-    <row r="59" spans="6:7">
+    <row r="59" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
     </row>
-    <row r="60" spans="6:7">
+    <row r="60" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
     </row>
-    <row r="61" spans="6:7">
+    <row r="61" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>